--- a/Datos Experimentales/Data 24026.xlsx
+++ b/Datos Experimentales/Data 24026.xlsx
@@ -1,7 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cltor\Documents\SB_Calibration_2025\Datos Experimentales\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA5AC69D-AA4B-4E34-805E-21C10F00F462}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="2" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Antecedentes_info" sheetId="1" r:id="rId1"/>
     <sheet name="Antecedentes" sheetId="2" r:id="rId2"/>
@@ -18,6 +28,7 @@
     <sheet name="Manual Densidades" sheetId="13" r:id="rId13"/>
     <sheet name="Winegrid densidad" sheetId="14" r:id="rId14"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -1263,11 +1274,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1296,14 +1304,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -1628,10 +1645,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B119"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1639,7 +1657,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1647,7 +1665,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1655,7 +1673,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1663,7 +1681,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -1671,7 +1689,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -1679,7 +1697,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1687,7 +1705,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -1695,7 +1713,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -1703,7 +1721,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -1711,7 +1729,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -1719,7 +1737,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -1727,7 +1745,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>15</v>
       </c>
@@ -1735,7 +1753,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>16</v>
       </c>
@@ -1743,7 +1761,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>17</v>
       </c>
@@ -1751,7 +1769,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -1759,7 +1777,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>19</v>
       </c>
@@ -1767,7 +1785,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>20</v>
       </c>
@@ -1775,7 +1793,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>21</v>
       </c>
@@ -1783,7 +1801,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>22</v>
       </c>
@@ -1791,7 +1809,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>23</v>
       </c>
@@ -1799,7 +1817,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>24</v>
       </c>
@@ -1807,7 +1825,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>25</v>
       </c>
@@ -1815,7 +1833,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>26</v>
       </c>
@@ -1823,7 +1841,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>27</v>
       </c>
@@ -1831,7 +1849,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>28</v>
       </c>
@@ -1839,7 +1857,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>29</v>
       </c>
@@ -1847,7 +1865,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>30</v>
       </c>
@@ -1855,7 +1873,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>31</v>
       </c>
@@ -1863,7 +1881,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>33</v>
       </c>
@@ -1871,7 +1889,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>34</v>
       </c>
@@ -1879,7 +1897,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>35</v>
       </c>
@@ -1887,7 +1905,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>36</v>
       </c>
@@ -1895,7 +1913,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>37</v>
       </c>
@@ -1903,7 +1921,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>39</v>
       </c>
@@ -1911,7 +1929,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>40</v>
       </c>
@@ -1919,7 +1937,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>41</v>
       </c>
@@ -1927,7 +1945,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>42</v>
       </c>
@@ -1935,7 +1953,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>43</v>
       </c>
@@ -1943,7 +1961,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>44</v>
       </c>
@@ -1951,7 +1969,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>45</v>
       </c>
@@ -1959,7 +1977,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>46</v>
       </c>
@@ -1967,7 +1985,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>47</v>
       </c>
@@ -1975,7 +1993,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>49</v>
       </c>
@@ -1983,7 +2001,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>50</v>
       </c>
@@ -1991,7 +2009,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>51</v>
       </c>
@@ -1999,7 +2017,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>52</v>
       </c>
@@ -2007,7 +2025,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>54</v>
       </c>
@@ -2015,7 +2033,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>55</v>
       </c>
@@ -2023,7 +2041,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>56</v>
       </c>
@@ -2031,7 +2049,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>57</v>
       </c>
@@ -2039,7 +2057,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>58</v>
       </c>
@@ -2047,7 +2065,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>59</v>
       </c>
@@ -2055,7 +2073,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>61</v>
       </c>
@@ -2063,7 +2081,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>62</v>
       </c>
@@ -2071,7 +2089,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>63</v>
       </c>
@@ -2079,7 +2097,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>64</v>
       </c>
@@ -2087,7 +2105,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>65</v>
       </c>
@@ -2095,7 +2113,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>67</v>
       </c>
@@ -2103,7 +2121,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>68</v>
       </c>
@@ -2111,7 +2129,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>69</v>
       </c>
@@ -2119,7 +2137,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>70</v>
       </c>
@@ -2127,7 +2145,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>71</v>
       </c>
@@ -2135,7 +2153,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>72</v>
       </c>
@@ -2143,7 +2161,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>73</v>
       </c>
@@ -2151,7 +2169,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>74</v>
       </c>
@@ -2159,7 +2177,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>75</v>
       </c>
@@ -2167,7 +2185,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>77</v>
       </c>
@@ -2175,7 +2193,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>78</v>
       </c>
@@ -2183,7 +2201,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>79</v>
       </c>
@@ -2191,7 +2209,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>80</v>
       </c>
@@ -2199,7 +2217,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>81</v>
       </c>
@@ -2207,7 +2225,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>82</v>
       </c>
@@ -2215,7 +2233,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>83</v>
       </c>
@@ -2223,7 +2241,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>84</v>
       </c>
@@ -2231,7 +2249,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>85</v>
       </c>
@@ -2239,7 +2257,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>86</v>
       </c>
@@ -2247,7 +2265,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>87</v>
       </c>
@@ -2255,7 +2273,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>88</v>
       </c>
@@ -2263,7 +2281,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>89</v>
       </c>
@@ -2271,7 +2289,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>90</v>
       </c>
@@ -2279,7 +2297,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>92</v>
       </c>
@@ -2287,7 +2305,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>93</v>
       </c>
@@ -2295,7 +2313,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>94</v>
       </c>
@@ -2303,7 +2321,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>96</v>
       </c>
@@ -2311,7 +2329,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>97</v>
       </c>
@@ -2319,7 +2337,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>98</v>
       </c>
@@ -2327,7 +2345,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>99</v>
       </c>
@@ -2335,7 +2353,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>100</v>
       </c>
@@ -2343,7 +2361,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>101</v>
       </c>
@@ -2351,7 +2369,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>102</v>
       </c>
@@ -2359,7 +2377,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>103</v>
       </c>
@@ -2367,7 +2385,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>104</v>
       </c>
@@ -2375,7 +2393,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>105</v>
       </c>
@@ -2383,7 +2401,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>106</v>
       </c>
@@ -2391,7 +2409,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>107</v>
       </c>
@@ -2399,7 +2417,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="97">
+    <row r="97" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>108</v>
       </c>
@@ -2407,7 +2425,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="98">
+    <row r="98" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>109</v>
       </c>
@@ -2415,7 +2433,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="99">
+    <row r="99" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>110</v>
       </c>
@@ -2423,7 +2441,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>112</v>
       </c>
@@ -2431,7 +2449,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>113</v>
       </c>
@@ -2439,7 +2457,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="102">
+    <row r="102" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>114</v>
       </c>
@@ -2447,7 +2465,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="103">
+    <row r="103" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>115</v>
       </c>
@@ -2455,7 +2473,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="104">
+    <row r="104" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>116</v>
       </c>
@@ -2463,7 +2481,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="105">
+    <row r="105" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>117</v>
       </c>
@@ -2471,7 +2489,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="106">
+    <row r="106" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>118</v>
       </c>
@@ -2479,7 +2497,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="107">
+    <row r="107" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>119</v>
       </c>
@@ -2487,7 +2505,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="108">
+    <row r="108" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>120</v>
       </c>
@@ -2495,7 +2513,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="109">
+    <row r="109" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>121</v>
       </c>
@@ -2503,7 +2521,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="110">
+    <row r="110" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>122</v>
       </c>
@@ -2511,7 +2529,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="111">
+    <row r="111" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>123</v>
       </c>
@@ -2519,7 +2537,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="112">
+    <row r="112" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>124</v>
       </c>
@@ -2527,7 +2545,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="113">
+    <row r="113" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>125</v>
       </c>
@@ -2535,7 +2553,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="114">
+    <row r="114" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>126</v>
       </c>
@@ -2543,7 +2561,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="115">
+    <row r="115" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>128</v>
       </c>
@@ -2551,7 +2569,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="116">
+    <row r="116" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>129</v>
       </c>
@@ -2559,7 +2577,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="117">
+    <row r="117" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>130</v>
       </c>
@@ -2567,7 +2585,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="118">
+    <row r="118" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>131</v>
       </c>
@@ -2575,7 +2593,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="119">
+    <row r="119" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>132</v>
       </c>
@@ -2584,27 +2602,31 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B119"/>
+    <ignoredError sqref="A1:B119" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1"/>
+    <ignoredError sqref="A1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:F1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>279</v>
       </c>
@@ -2625,17 +2647,19 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1"/>
+    <ignoredError sqref="A1:F1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:C124"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>284</v>
       </c>
@@ -2646,95 +2670,95 @@
         <v>286</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>287</v>
       </c>
       <c r="B2">
-        <v>0.2222222222222222</v>
+        <v>0.22222222222222221</v>
       </c>
       <c r="C2">
         <v>14</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>288</v>
       </c>
       <c r="B3">
-        <v>0.4722222222222222</v>
+        <v>0.47222222222222221</v>
       </c>
       <c r="C3">
         <v>13</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>289</v>
       </c>
       <c r="B4">
-        <v>0.7222222222222222</v>
+        <v>0.72222222222222221</v>
       </c>
       <c r="C4">
         <v>13</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>290</v>
       </c>
       <c r="B5">
-        <v>0.9722222222222222</v>
+        <v>0.97222222222222221</v>
       </c>
       <c r="C5">
         <v>13</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>291</v>
       </c>
       <c r="B6">
-        <v>1.222222222222222</v>
+        <v>1.2222222222222221</v>
       </c>
       <c r="C6">
         <v>13</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>292</v>
       </c>
       <c r="B7">
-        <v>1.472222222222222</v>
+        <v>1.4722222222222221</v>
       </c>
       <c r="C7">
         <v>13</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>293</v>
       </c>
       <c r="B8">
-        <v>1.722222222222222</v>
+        <v>1.7222222222222221</v>
       </c>
       <c r="C8">
         <v>12.5</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>294</v>
       </c>
       <c r="B9">
-        <v>1.972222222222222</v>
+        <v>1.9722222222222221</v>
       </c>
       <c r="C9">
         <v>13</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>295</v>
       </c>
@@ -2745,7 +2769,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>296</v>
       </c>
@@ -2756,7 +2780,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>297</v>
       </c>
@@ -2767,7 +2791,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>298</v>
       </c>
@@ -2778,7 +2802,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>299</v>
       </c>
@@ -2789,7 +2813,7 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>300</v>
       </c>
@@ -2800,7 +2824,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>301</v>
       </c>
@@ -2811,7 +2835,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>302</v>
       </c>
@@ -2822,282 +2846,282 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>303</v>
       </c>
       <c r="B18">
-        <v>4.222222222222222</v>
+        <v>4.2222222222222223</v>
       </c>
       <c r="C18">
         <v>12.5</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>303</v>
       </c>
       <c r="B19">
-        <v>4.222222222222222</v>
+        <v>4.2222222222222223</v>
       </c>
       <c r="C19">
         <v>12.5</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>304</v>
       </c>
       <c r="B20">
-        <v>4.472222222222222</v>
+        <v>4.4722222222222223</v>
       </c>
       <c r="C20">
         <v>13</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>305</v>
       </c>
       <c r="B21">
-        <v>4.722222222222222</v>
+        <v>4.7222222222222223</v>
       </c>
       <c r="C21">
         <v>13</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>306</v>
       </c>
       <c r="B22">
-        <v>4.972222222222222</v>
+        <v>4.9722222222222223</v>
       </c>
       <c r="C22">
         <v>13</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>307</v>
       </c>
       <c r="B23">
-        <v>5.222222222222222</v>
+        <v>5.2222222222222223</v>
       </c>
       <c r="C23">
         <v>12.6</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>308</v>
       </c>
       <c r="B24">
-        <v>5.472222222222222</v>
+        <v>5.4722222222222223</v>
       </c>
       <c r="C24">
         <v>13</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>309</v>
       </c>
       <c r="B25">
-        <v>5.722222222222222</v>
+        <v>5.7222222222222223</v>
       </c>
       <c r="C25">
         <v>12.5</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>310</v>
       </c>
       <c r="B26">
-        <v>5.972222222222222</v>
+        <v>5.9722222222222223</v>
       </c>
       <c r="C26">
         <v>13</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>311</v>
       </c>
       <c r="B27">
-        <v>6.222222222222222</v>
+        <v>6.2222222222222223</v>
       </c>
       <c r="C27">
         <v>12.7</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>312</v>
       </c>
       <c r="B28">
-        <v>6.472222222222222</v>
+        <v>6.4722222222222223</v>
       </c>
       <c r="C28">
         <v>13</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>313</v>
       </c>
       <c r="B29">
-        <v>6.722222222222222</v>
+        <v>6.7222222222222223</v>
       </c>
       <c r="C29">
         <v>15</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>314</v>
       </c>
       <c r="B30">
-        <v>6.972222222222222</v>
+        <v>6.9722222222222223</v>
       </c>
       <c r="C30">
         <v>13</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>315</v>
       </c>
       <c r="B31">
-        <v>7.222222222222222</v>
+        <v>7.2222222222222223</v>
       </c>
       <c r="C31">
         <v>38.4</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>316</v>
       </c>
       <c r="B32">
-        <v>7.472222222222222</v>
+        <v>7.4722222222222223</v>
       </c>
       <c r="C32">
         <v>12.6</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>317</v>
       </c>
       <c r="B33">
-        <v>7.722222222222222</v>
+        <v>7.7222222222222223</v>
       </c>
       <c r="C33">
         <v>13</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>318</v>
       </c>
       <c r="B34">
-        <v>7.972222222222222</v>
+        <v>7.9722222222222223</v>
       </c>
       <c r="C34">
         <v>13.1</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>319</v>
       </c>
       <c r="B35">
-        <v>8.222222222222221</v>
+        <v>8.2222222222222214</v>
       </c>
       <c r="C35">
         <v>12.7</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>320</v>
       </c>
       <c r="B36">
-        <v>8.472222222222221</v>
+        <v>8.4722222222222214</v>
       </c>
       <c r="C36">
         <v>13.2</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>321</v>
       </c>
       <c r="B37">
-        <v>8.722222222222221</v>
+        <v>8.7222222222222214</v>
       </c>
       <c r="C37">
         <v>13.6</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>322</v>
       </c>
       <c r="B38">
-        <v>8.930555555555555</v>
+        <v>8.9305555555555554</v>
       </c>
       <c r="C38">
         <v>12.5</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>323</v>
       </c>
       <c r="B39">
-        <v>9.222222222222221</v>
+        <v>9.2222222222222214</v>
       </c>
       <c r="C39">
         <v>13</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>324</v>
       </c>
       <c r="B40">
-        <v>9.472222222222221</v>
+        <v>9.4722222222222214</v>
       </c>
       <c r="C40">
         <v>13</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>325</v>
       </c>
       <c r="B41">
-        <v>9.722222222222221</v>
+        <v>9.7222222222222214</v>
       </c>
       <c r="C41">
         <v>12.7</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>326</v>
       </c>
       <c r="B42">
-        <v>9.972222222222221</v>
+        <v>9.9722222222222214</v>
       </c>
       <c r="C42">
         <v>12.8</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>327</v>
       </c>
@@ -3108,7 +3132,7 @@
         <v>13.4</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>328</v>
       </c>
@@ -3119,7 +3143,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>329</v>
       </c>
@@ -3130,7 +3154,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>330</v>
       </c>
@@ -3141,7 +3165,7 @@
         <v>12.8</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>331</v>
       </c>
@@ -3152,7 +3176,7 @@
         <v>13.4</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>332</v>
       </c>
@@ -3163,7 +3187,7 @@
         <v>13.1</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>333</v>
       </c>
@@ -3174,7 +3198,7 @@
         <v>13.3</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>334</v>
       </c>
@@ -3185,7 +3209,7 @@
         <v>12.8</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>335</v>
       </c>
@@ -3196,7 +3220,7 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>336</v>
       </c>
@@ -3207,7 +3231,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>337</v>
       </c>
@@ -3218,7 +3242,7 @@
         <v>13.1</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>338</v>
       </c>
@@ -3229,7 +3253,7 @@
         <v>13.1</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>339</v>
       </c>
@@ -3240,7 +3264,7 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>340</v>
       </c>
@@ -3251,7 +3275,7 @@
         <v>13.2</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>341</v>
       </c>
@@ -3262,7 +3286,7 @@
         <v>13.2</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>342</v>
       </c>
@@ -3273,7 +3297,7 @@
         <v>12.8</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>343</v>
       </c>
@@ -3284,7 +3308,7 @@
         <v>12.8</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>344</v>
       </c>
@@ -3295,7 +3319,7 @@
         <v>13.2</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>345</v>
       </c>
@@ -3306,7 +3330,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>346</v>
       </c>
@@ -3317,7 +3341,7 @@
         <v>13.2</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>347</v>
       </c>
@@ -3328,7 +3352,7 @@
         <v>13.4</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>348</v>
       </c>
@@ -3339,7 +3363,7 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>349</v>
       </c>
@@ -3350,7 +3374,7 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>350</v>
       </c>
@@ -3361,656 +3385,658 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>351</v>
       </c>
       <c r="B67">
-        <v>16.22222222222222</v>
+        <v>16.222222222222221</v>
       </c>
       <c r="C67">
         <v>13.2</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>352</v>
       </c>
       <c r="B68">
-        <v>16.47222222222222</v>
+        <v>16.472222222222221</v>
       </c>
       <c r="C68">
         <v>13.4</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>353</v>
       </c>
       <c r="B69">
-        <v>16.72222222222222</v>
+        <v>16.722222222222221</v>
       </c>
       <c r="C69">
         <v>13.3</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>354</v>
       </c>
       <c r="B70">
-        <v>16.97222222222222</v>
+        <v>16.972222222222221</v>
       </c>
       <c r="C70">
         <v>12.8</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>355</v>
       </c>
       <c r="B71">
-        <v>17.22222222222222</v>
+        <v>17.222222222222221</v>
       </c>
       <c r="C71">
         <v>13</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>356</v>
       </c>
       <c r="B72">
-        <v>17.47222222222222</v>
+        <v>17.472222222222221</v>
       </c>
       <c r="C72">
         <v>12.7</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>357</v>
       </c>
       <c r="B73">
-        <v>17.72222222222222</v>
+        <v>17.722222222222221</v>
       </c>
       <c r="C73">
         <v>12.6</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>358</v>
       </c>
       <c r="B74">
-        <v>17.97222222222222</v>
+        <v>17.972222222222221</v>
       </c>
       <c r="C74">
         <v>12.8</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>359</v>
       </c>
       <c r="B75">
-        <v>18.22222222222222</v>
+        <v>18.222222222222221</v>
       </c>
       <c r="C75">
         <v>13.2</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>360</v>
       </c>
       <c r="B76">
-        <v>18.47222222222222</v>
+        <v>18.472222222222221</v>
       </c>
       <c r="C76">
         <v>12.7</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>361</v>
       </c>
       <c r="B77">
-        <v>18.72222222222222</v>
+        <v>18.722222222222221</v>
       </c>
       <c r="C77">
         <v>13.2</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>362</v>
       </c>
       <c r="B78">
-        <v>18.97222222222222</v>
+        <v>18.972222222222221</v>
       </c>
       <c r="C78">
         <v>13</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>363</v>
       </c>
       <c r="B79">
-        <v>19.22222222222222</v>
+        <v>19.222222222222221</v>
       </c>
       <c r="C79">
         <v>13.5</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>364</v>
       </c>
       <c r="B80">
-        <v>19.47222222222222</v>
+        <v>19.472222222222221</v>
       </c>
       <c r="C80">
         <v>13.4</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>365</v>
       </c>
       <c r="B81">
-        <v>19.72222222222222</v>
+        <v>19.722222222222221</v>
       </c>
       <c r="C81">
         <v>13.4</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>366</v>
       </c>
       <c r="B82">
-        <v>20.22222222222222</v>
+        <v>20.222222222222221</v>
       </c>
       <c r="C82">
         <v>12.7</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>367</v>
       </c>
       <c r="B83">
-        <v>20.47222222222222</v>
+        <v>20.472222222222221</v>
       </c>
       <c r="C83">
         <v>13.1</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>368</v>
       </c>
       <c r="B84">
-        <v>20.97222222222222</v>
+        <v>20.972222222222221</v>
       </c>
       <c r="C84">
         <v>12.6</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>369</v>
       </c>
       <c r="B85">
-        <v>21.22222222222222</v>
+        <v>21.222222222222221</v>
       </c>
       <c r="C85">
         <v>13.1</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>370</v>
       </c>
       <c r="B86">
-        <v>21.47222222222222</v>
+        <v>21.472222222222221</v>
       </c>
       <c r="C86">
         <v>12.6</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>371</v>
       </c>
       <c r="B87">
-        <v>21.72222222222222</v>
+        <v>21.722222222222221</v>
       </c>
       <c r="C87">
         <v>13.2</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>372</v>
       </c>
       <c r="B88">
-        <v>21.97222222222222</v>
+        <v>21.972222222222221</v>
       </c>
       <c r="C88">
         <v>12.8</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>373</v>
       </c>
       <c r="B89">
-        <v>22.22222222222222</v>
+        <v>22.222222222222221</v>
       </c>
       <c r="C89">
         <v>13.3</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>374</v>
       </c>
       <c r="B90">
-        <v>22.47222222222222</v>
+        <v>22.472222222222221</v>
       </c>
       <c r="C90">
         <v>12.7</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>375</v>
       </c>
       <c r="B91">
-        <v>22.72222222222222</v>
+        <v>22.722222222222221</v>
       </c>
       <c r="C91">
         <v>13.5</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>376</v>
       </c>
       <c r="B92">
-        <v>22.97222222222222</v>
+        <v>22.972222222222221</v>
       </c>
       <c r="C92">
         <v>12.8</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>377</v>
       </c>
       <c r="B93">
-        <v>23.22222222222222</v>
+        <v>23.222222222222221</v>
       </c>
       <c r="C93">
         <v>12.7</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>378</v>
       </c>
       <c r="B94">
-        <v>23.47222222222222</v>
+        <v>23.472222222222221</v>
       </c>
       <c r="C94">
         <v>12.9</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>379</v>
       </c>
       <c r="B95">
-        <v>23.72222222222222</v>
+        <v>23.722222222222221</v>
       </c>
       <c r="C95">
         <v>13</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>380</v>
       </c>
       <c r="B96">
-        <v>23.97222222222222</v>
+        <v>23.972222222222221</v>
       </c>
       <c r="C96">
         <v>13</v>
       </c>
     </row>
-    <row r="97">
+    <row r="97" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>381</v>
       </c>
       <c r="B97">
-        <v>24.22222222222222</v>
+        <v>24.222222222222221</v>
       </c>
       <c r="C97">
         <v>12.7</v>
       </c>
     </row>
-    <row r="98">
+    <row r="98" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>382</v>
       </c>
       <c r="B98">
-        <v>24.47222222222222</v>
+        <v>24.472222222222221</v>
       </c>
       <c r="C98">
         <v>13.1</v>
       </c>
     </row>
-    <row r="99">
+    <row r="99" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>383</v>
       </c>
       <c r="B99">
-        <v>24.72222222222222</v>
+        <v>24.722222222222221</v>
       </c>
       <c r="C99">
         <v>12.9</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>384</v>
       </c>
       <c r="B100">
-        <v>24.97222222222222</v>
+        <v>24.972222222222221</v>
       </c>
       <c r="C100">
         <v>19.8</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>385</v>
       </c>
       <c r="B101">
-        <v>25.22222222222222</v>
+        <v>25.222222222222221</v>
       </c>
       <c r="C101">
-        <v>19.9</v>
-      </c>
-    </row>
-    <row r="102">
+        <v>19.899999999999999</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>386</v>
       </c>
       <c r="B102">
-        <v>25.47222222222222</v>
+        <v>25.472222222222221</v>
       </c>
       <c r="C102">
         <v>18.7</v>
       </c>
     </row>
-    <row r="103">
+    <row r="103" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>387</v>
       </c>
       <c r="B103">
-        <v>25.72222222222222</v>
+        <v>25.722222222222221</v>
       </c>
       <c r="C103">
         <v>19</v>
       </c>
     </row>
-    <row r="104">
+    <row r="104" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>388</v>
       </c>
       <c r="B104">
-        <v>25.97222222222222</v>
+        <v>25.972222222222221</v>
       </c>
       <c r="C104">
-        <v>19.4</v>
-      </c>
-    </row>
-    <row r="105">
+        <v>19.399999999999999</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>389</v>
       </c>
       <c r="B105">
-        <v>26.22222222222222</v>
+        <v>26.222222222222221</v>
       </c>
       <c r="C105">
         <v>20</v>
       </c>
     </row>
-    <row r="106">
+    <row r="106" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>390</v>
       </c>
       <c r="B106">
-        <v>26.47222222222222</v>
+        <v>26.472222222222221</v>
       </c>
       <c r="C106">
-        <v>19.4</v>
-      </c>
-    </row>
-    <row r="107">
+        <v>19.399999999999999</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>391</v>
       </c>
       <c r="B107">
-        <v>26.72222222222222</v>
+        <v>26.722222222222221</v>
       </c>
       <c r="C107">
-        <v>18.9</v>
-      </c>
-    </row>
-    <row r="108">
+        <v>18.899999999999999</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>392</v>
       </c>
       <c r="B108">
-        <v>26.97222222222222</v>
+        <v>26.972222222222221</v>
       </c>
       <c r="C108">
-        <v>19.1</v>
-      </c>
-    </row>
-    <row r="109">
+        <v>19.100000000000001</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>393</v>
       </c>
       <c r="B109">
-        <v>27.22222222222222</v>
+        <v>27.222222222222221</v>
       </c>
       <c r="C109">
         <v>20.2</v>
       </c>
     </row>
-    <row r="110">
+    <row r="110" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>394</v>
       </c>
       <c r="B110">
-        <v>27.47222222222222</v>
+        <v>27.472222222222221</v>
       </c>
       <c r="C110">
         <v>20</v>
       </c>
     </row>
-    <row r="111">
+    <row r="111" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>395</v>
       </c>
       <c r="B111">
-        <v>27.72222222222222</v>
+        <v>27.722222222222221</v>
       </c>
       <c r="C111">
         <v>19.7</v>
       </c>
     </row>
-    <row r="112">
+    <row r="112" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>396</v>
       </c>
       <c r="B112">
-        <v>27.97222222222222</v>
+        <v>27.972222222222221</v>
       </c>
       <c r="C112">
         <v>19.8</v>
       </c>
     </row>
-    <row r="113">
+    <row r="113" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>397</v>
       </c>
       <c r="B113">
-        <v>28.22222222222222</v>
+        <v>28.222222222222221</v>
       </c>
       <c r="C113">
-        <v>19.9</v>
-      </c>
-    </row>
-    <row r="114">
+        <v>19.899999999999999</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>398</v>
       </c>
       <c r="B114">
-        <v>28.47222222222222</v>
+        <v>28.472222222222221</v>
       </c>
       <c r="C114">
         <v>19.5</v>
       </c>
     </row>
-    <row r="115">
+    <row r="115" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>399</v>
       </c>
       <c r="B115">
-        <v>28.72222222222222</v>
+        <v>28.722222222222221</v>
       </c>
       <c r="C115">
-        <v>19.1</v>
-      </c>
-    </row>
-    <row r="116">
+        <v>19.100000000000001</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>400</v>
       </c>
       <c r="B116">
-        <v>28.97222222222222</v>
+        <v>28.972222222222221</v>
       </c>
       <c r="C116">
         <v>19.2</v>
       </c>
     </row>
-    <row r="117">
+    <row r="117" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>401</v>
       </c>
       <c r="B117">
-        <v>29.22222222222222</v>
+        <v>29.222222222222221</v>
       </c>
       <c r="C117">
         <v>19.2</v>
       </c>
     </row>
-    <row r="118">
+    <row r="118" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>402</v>
       </c>
       <c r="B118">
-        <v>29.47222222222222</v>
+        <v>29.472222222222221</v>
       </c>
       <c r="C118">
-        <v>18.9</v>
-      </c>
-    </row>
-    <row r="119">
+        <v>18.899999999999999</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>403</v>
       </c>
       <c r="B119">
-        <v>29.72222222222222</v>
+        <v>29.722222222222221</v>
       </c>
       <c r="C119">
         <v>19.2</v>
       </c>
     </row>
-    <row r="120">
+    <row r="120" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>404</v>
       </c>
       <c r="B120">
-        <v>29.97222222222222</v>
+        <v>29.972222222222221</v>
       </c>
       <c r="C120">
         <v>26.5</v>
       </c>
     </row>
-    <row r="121">
+    <row r="121" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>405</v>
       </c>
       <c r="B121">
-        <v>30.22222222222222</v>
+        <v>30.222222222222221</v>
       </c>
       <c r="C121">
         <v>20</v>
       </c>
     </row>
-    <row r="122">
+    <row r="122" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>406</v>
       </c>
       <c r="B122">
-        <v>30.47222222222222</v>
+        <v>30.472222222222221</v>
       </c>
       <c r="C122">
         <v>19.7</v>
       </c>
     </row>
-    <row r="123">
+    <row r="123" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>407</v>
       </c>
       <c r="B123">
-        <v>30.72222222222222</v>
+        <v>30.722222222222221</v>
       </c>
       <c r="C123">
-        <v>18.6</v>
-      </c>
-    </row>
-    <row r="124">
+        <v>18.600000000000001</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>408</v>
       </c>
       <c r="B124">
-        <v>30.97222222222222</v>
+        <v>30.972222222222221</v>
       </c>
       <c r="C124">
-        <v>19.1</v>
+        <v>19.100000000000001</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C124"/>
+    <ignoredError sqref="A1:C124" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:C124"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>284</v>
       </c>
@@ -4021,95 +4047,95 @@
         <v>177</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>287</v>
       </c>
       <c r="B2">
-        <v>0.2222222222222222</v>
+        <v>0.22222222222222221</v>
       </c>
       <c r="C2">
         <v>1087</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>288</v>
       </c>
       <c r="B3">
-        <v>0.4722222222222222</v>
+        <v>0.47222222222222221</v>
       </c>
       <c r="C3">
         <v>1086</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>289</v>
       </c>
       <c r="B4">
-        <v>0.7222222222222222</v>
+        <v>0.72222222222222221</v>
       </c>
       <c r="C4">
         <v>1086</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>290</v>
       </c>
       <c r="B5">
-        <v>0.9722222222222222</v>
+        <v>0.97222222222222221</v>
       </c>
       <c r="C5">
         <v>1086</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>291</v>
       </c>
       <c r="B6">
-        <v>1.222222222222222</v>
+        <v>1.2222222222222221</v>
       </c>
       <c r="C6">
         <v>1086</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>292</v>
       </c>
       <c r="B7">
-        <v>1.472222222222222</v>
+        <v>1.4722222222222221</v>
       </c>
       <c r="C7">
         <v>1085</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>293</v>
       </c>
       <c r="B8">
-        <v>1.722222222222222</v>
+        <v>1.7222222222222221</v>
       </c>
       <c r="C8">
         <v>1084</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>294</v>
       </c>
       <c r="B9">
-        <v>1.972222222222222</v>
+        <v>1.9722222222222221</v>
       </c>
       <c r="C9">
         <v>1083</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>295</v>
       </c>
@@ -4120,7 +4146,7 @@
         <v>1083</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>296</v>
       </c>
@@ -4131,7 +4157,7 @@
         <v>1080</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>297</v>
       </c>
@@ -4142,7 +4168,7 @@
         <v>1079</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>298</v>
       </c>
@@ -4153,7 +4179,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>299</v>
       </c>
@@ -4164,7 +4190,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>300</v>
       </c>
@@ -4175,7 +4201,7 @@
         <v>1071</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>301</v>
       </c>
@@ -4186,7 +4212,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>302</v>
       </c>
@@ -4197,282 +4223,282 @@
         <v>1066</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>303</v>
       </c>
       <c r="B18">
-        <v>4.222222222222222</v>
+        <v>4.2222222222222223</v>
       </c>
       <c r="C18">
         <v>1060</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>303</v>
       </c>
       <c r="B19">
-        <v>4.222222222222222</v>
+        <v>4.2222222222222223</v>
       </c>
       <c r="C19">
         <v>1060</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>304</v>
       </c>
       <c r="B20">
-        <v>4.472222222222222</v>
+        <v>4.4722222222222223</v>
       </c>
       <c r="C20">
         <v>1056</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>305</v>
       </c>
       <c r="B21">
-        <v>4.722222222222222</v>
+        <v>4.7222222222222223</v>
       </c>
       <c r="C21">
         <v>1053</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>306</v>
       </c>
       <c r="B22">
-        <v>4.972222222222222</v>
+        <v>4.9722222222222223</v>
       </c>
       <c r="C22">
         <v>1050</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>307</v>
       </c>
       <c r="B23">
-        <v>5.222222222222222</v>
+        <v>5.2222222222222223</v>
       </c>
       <c r="C23">
         <v>1046</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>308</v>
       </c>
       <c r="B24">
-        <v>5.472222222222222</v>
+        <v>5.4722222222222223</v>
       </c>
       <c r="C24">
         <v>1041</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>309</v>
       </c>
       <c r="B25">
-        <v>5.722222222222222</v>
+        <v>5.7222222222222223</v>
       </c>
       <c r="C25">
         <v>1039</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>310</v>
       </c>
       <c r="B26">
-        <v>5.972222222222222</v>
+        <v>5.9722222222222223</v>
       </c>
       <c r="C26">
         <v>1036</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>311</v>
       </c>
       <c r="B27">
-        <v>6.222222222222222</v>
+        <v>6.2222222222222223</v>
       </c>
       <c r="C27">
         <v>1033</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>312</v>
       </c>
       <c r="B28">
-        <v>6.472222222222222</v>
+        <v>6.4722222222222223</v>
       </c>
       <c r="C28">
         <v>1029</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>313</v>
       </c>
       <c r="B29">
-        <v>6.722222222222222</v>
+        <v>6.7222222222222223</v>
       </c>
       <c r="C29">
         <v>1027</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>314</v>
       </c>
       <c r="B30">
-        <v>6.972222222222222</v>
+        <v>6.9722222222222223</v>
       </c>
       <c r="C30">
         <v>1029</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>315</v>
       </c>
       <c r="B31">
-        <v>7.222222222222222</v>
+        <v>7.2222222222222223</v>
       </c>
       <c r="C31">
         <v>1015</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>316</v>
       </c>
       <c r="B32">
-        <v>7.472222222222222</v>
+        <v>7.4722222222222223</v>
       </c>
       <c r="C32">
         <v>1017</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>317</v>
       </c>
       <c r="B33">
-        <v>7.722222222222222</v>
+        <v>7.7222222222222223</v>
       </c>
       <c r="C33">
         <v>1016</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>318</v>
       </c>
       <c r="B34">
-        <v>7.972222222222222</v>
+        <v>7.9722222222222223</v>
       </c>
       <c r="C34">
         <v>1015</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>319</v>
       </c>
       <c r="B35">
-        <v>8.222222222222221</v>
+        <v>8.2222222222222214</v>
       </c>
       <c r="C35">
         <v>1015</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>320</v>
       </c>
       <c r="B36">
-        <v>8.472222222222221</v>
+        <v>8.4722222222222214</v>
       </c>
       <c r="C36">
         <v>1014</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>321</v>
       </c>
       <c r="B37">
-        <v>8.722222222222221</v>
+        <v>8.7222222222222214</v>
       </c>
       <c r="C37">
         <v>1014</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>322</v>
       </c>
       <c r="B38">
-        <v>8.930555555555555</v>
+        <v>8.9305555555555554</v>
       </c>
       <c r="C38">
         <v>1014</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>323</v>
       </c>
       <c r="B39">
-        <v>9.222222222222221</v>
+        <v>9.2222222222222214</v>
       </c>
       <c r="C39">
         <v>1013</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>324</v>
       </c>
       <c r="B40">
-        <v>9.472222222222221</v>
+        <v>9.4722222222222214</v>
       </c>
       <c r="C40">
         <v>1012</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>325</v>
       </c>
       <c r="B41">
-        <v>9.722222222222221</v>
+        <v>9.7222222222222214</v>
       </c>
       <c r="C41">
         <v>1011</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>326</v>
       </c>
       <c r="B42">
-        <v>9.972222222222221</v>
+        <v>9.9722222222222214</v>
       </c>
       <c r="C42">
         <v>1010</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>327</v>
       </c>
@@ -4483,7 +4509,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>328</v>
       </c>
@@ -4494,7 +4520,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>329</v>
       </c>
@@ -4505,7 +4531,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>330</v>
       </c>
@@ -4516,7 +4542,7 @@
         <v>1009</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>331</v>
       </c>
@@ -4527,7 +4553,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>332</v>
       </c>
@@ -4538,7 +4564,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>333</v>
       </c>
@@ -4549,7 +4575,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>334</v>
       </c>
@@ -4560,7 +4586,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>335</v>
       </c>
@@ -4571,7 +4597,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>336</v>
       </c>
@@ -4582,7 +4608,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>337</v>
       </c>
@@ -4593,7 +4619,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>338</v>
       </c>
@@ -4604,7 +4630,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>339</v>
       </c>
@@ -4615,7 +4641,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>340</v>
       </c>
@@ -4626,7 +4652,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>341</v>
       </c>
@@ -4637,7 +4663,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>342</v>
       </c>
@@ -4648,7 +4674,7 @@
         <v>1004</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>343</v>
       </c>
@@ -4659,7 +4685,7 @@
         <v>1004</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>344</v>
       </c>
@@ -4670,7 +4696,7 @@
         <v>1004</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>345</v>
       </c>
@@ -4681,7 +4707,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>346</v>
       </c>
@@ -4692,7 +4718,7 @@
         <v>1004</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>347</v>
       </c>
@@ -4703,7 +4729,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>348</v>
       </c>
@@ -4714,7 +4740,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>349</v>
       </c>
@@ -4725,7 +4751,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>350</v>
       </c>
@@ -4736,656 +4762,658 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>351</v>
       </c>
       <c r="B67">
-        <v>16.22222222222222</v>
+        <v>16.222222222222221</v>
       </c>
       <c r="C67">
         <v>1002</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>352</v>
       </c>
       <c r="B68">
-        <v>16.47222222222222</v>
+        <v>16.472222222222221</v>
       </c>
       <c r="C68">
         <v>1002</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>353</v>
       </c>
       <c r="B69">
-        <v>16.72222222222222</v>
+        <v>16.722222222222221</v>
       </c>
       <c r="C69">
         <v>1002</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>354</v>
       </c>
       <c r="B70">
-        <v>16.97222222222222</v>
+        <v>16.972222222222221</v>
       </c>
       <c r="C70">
         <v>1002</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>355</v>
       </c>
       <c r="B71">
-        <v>17.22222222222222</v>
+        <v>17.222222222222221</v>
       </c>
       <c r="C71">
         <v>1001</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>356</v>
       </c>
       <c r="B72">
-        <v>17.47222222222222</v>
+        <v>17.472222222222221</v>
       </c>
       <c r="C72">
         <v>1001</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>357</v>
       </c>
       <c r="B73">
-        <v>17.72222222222222</v>
+        <v>17.722222222222221</v>
       </c>
       <c r="C73">
         <v>1001</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>358</v>
       </c>
       <c r="B74">
-        <v>17.97222222222222</v>
+        <v>17.972222222222221</v>
       </c>
       <c r="C74">
         <v>1001</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>359</v>
       </c>
       <c r="B75">
-        <v>18.22222222222222</v>
+        <v>18.222222222222221</v>
       </c>
       <c r="C75">
         <v>1001</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>360</v>
       </c>
       <c r="B76">
-        <v>18.47222222222222</v>
+        <v>18.472222222222221</v>
       </c>
       <c r="C76">
         <v>998</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>361</v>
       </c>
       <c r="B77">
-        <v>18.72222222222222</v>
+        <v>18.722222222222221</v>
       </c>
       <c r="C77">
         <v>1001</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>362</v>
       </c>
       <c r="B78">
-        <v>18.97222222222222</v>
+        <v>18.972222222222221</v>
       </c>
       <c r="C78">
         <v>1000</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>363</v>
       </c>
       <c r="B79">
-        <v>19.22222222222222</v>
+        <v>19.222222222222221</v>
       </c>
       <c r="C79">
         <v>999</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>364</v>
       </c>
       <c r="B80">
-        <v>19.47222222222222</v>
+        <v>19.472222222222221</v>
       </c>
       <c r="C80">
         <v>999</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>365</v>
       </c>
       <c r="B81">
-        <v>19.72222222222222</v>
+        <v>19.722222222222221</v>
       </c>
       <c r="C81">
         <v>999</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>366</v>
       </c>
       <c r="B82">
-        <v>20.22222222222222</v>
+        <v>20.222222222222221</v>
       </c>
       <c r="C82">
         <v>999</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>367</v>
       </c>
       <c r="B83">
-        <v>20.47222222222222</v>
+        <v>20.472222222222221</v>
       </c>
       <c r="C83">
         <v>999</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>368</v>
       </c>
       <c r="B84">
-        <v>20.97222222222222</v>
+        <v>20.972222222222221</v>
       </c>
       <c r="C84">
         <v>999</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>369</v>
       </c>
       <c r="B85">
-        <v>21.22222222222222</v>
+        <v>21.222222222222221</v>
       </c>
       <c r="C85">
         <v>999</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>370</v>
       </c>
       <c r="B86">
-        <v>21.47222222222222</v>
+        <v>21.472222222222221</v>
       </c>
       <c r="C86">
         <v>998</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>371</v>
       </c>
       <c r="B87">
-        <v>21.72222222222222</v>
+        <v>21.722222222222221</v>
       </c>
       <c r="C87">
         <v>998</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>372</v>
       </c>
       <c r="B88">
-        <v>21.97222222222222</v>
+        <v>21.972222222222221</v>
       </c>
       <c r="C88">
         <v>998</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>373</v>
       </c>
       <c r="B89">
-        <v>22.22222222222222</v>
+        <v>22.222222222222221</v>
       </c>
       <c r="C89">
         <v>997</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>374</v>
       </c>
       <c r="B90">
-        <v>22.47222222222222</v>
+        <v>22.472222222222221</v>
       </c>
       <c r="C90">
         <v>997</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>375</v>
       </c>
       <c r="B91">
-        <v>22.72222222222222</v>
+        <v>22.722222222222221</v>
       </c>
       <c r="C91">
         <v>997</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>376</v>
       </c>
       <c r="B92">
-        <v>22.97222222222222</v>
+        <v>22.972222222222221</v>
       </c>
       <c r="C92">
         <v>997</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>377</v>
       </c>
       <c r="B93">
-        <v>23.22222222222222</v>
+        <v>23.222222222222221</v>
       </c>
       <c r="C93">
         <v>997</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>378</v>
       </c>
       <c r="B94">
-        <v>23.47222222222222</v>
+        <v>23.472222222222221</v>
       </c>
       <c r="C94">
         <v>997</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>379</v>
       </c>
       <c r="B95">
-        <v>23.72222222222222</v>
+        <v>23.722222222222221</v>
       </c>
       <c r="C95">
         <v>997</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>380</v>
       </c>
       <c r="B96">
-        <v>23.97222222222222</v>
+        <v>23.972222222222221</v>
       </c>
       <c r="C96">
         <v>997</v>
       </c>
     </row>
-    <row r="97">
+    <row r="97" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>381</v>
       </c>
       <c r="B97">
-        <v>24.22222222222222</v>
+        <v>24.222222222222221</v>
       </c>
       <c r="C97">
         <v>997</v>
       </c>
     </row>
-    <row r="98">
+    <row r="98" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>382</v>
       </c>
       <c r="B98">
-        <v>24.47222222222222</v>
+        <v>24.472222222222221</v>
       </c>
       <c r="C98">
         <v>997</v>
       </c>
     </row>
-    <row r="99">
+    <row r="99" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>383</v>
       </c>
       <c r="B99">
-        <v>24.72222222222222</v>
+        <v>24.722222222222221</v>
       </c>
       <c r="C99">
         <v>997</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>384</v>
       </c>
       <c r="B100">
-        <v>24.97222222222222</v>
+        <v>24.972222222222221</v>
       </c>
       <c r="C100">
         <v>996</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>385</v>
       </c>
       <c r="B101">
-        <v>25.22222222222222</v>
+        <v>25.222222222222221</v>
       </c>
       <c r="C101">
         <v>996</v>
       </c>
     </row>
-    <row r="102">
+    <row r="102" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>386</v>
       </c>
       <c r="B102">
-        <v>25.47222222222222</v>
+        <v>25.472222222222221</v>
       </c>
       <c r="C102">
         <v>996</v>
       </c>
     </row>
-    <row r="103">
+    <row r="103" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>387</v>
       </c>
       <c r="B103">
-        <v>25.72222222222222</v>
+        <v>25.722222222222221</v>
       </c>
       <c r="C103">
         <v>996</v>
       </c>
     </row>
-    <row r="104">
+    <row r="104" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>388</v>
       </c>
       <c r="B104">
-        <v>25.97222222222222</v>
+        <v>25.972222222222221</v>
       </c>
       <c r="C104">
         <v>994</v>
       </c>
     </row>
-    <row r="105">
+    <row r="105" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>389</v>
       </c>
       <c r="B105">
-        <v>26.22222222222222</v>
+        <v>26.222222222222221</v>
       </c>
       <c r="C105">
         <v>995</v>
       </c>
     </row>
-    <row r="106">
+    <row r="106" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>390</v>
       </c>
       <c r="B106">
-        <v>26.47222222222222</v>
+        <v>26.472222222222221</v>
       </c>
       <c r="C106">
         <v>995</v>
       </c>
     </row>
-    <row r="107">
+    <row r="107" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>391</v>
       </c>
       <c r="B107">
-        <v>26.72222222222222</v>
+        <v>26.722222222222221</v>
       </c>
       <c r="C107">
         <v>994</v>
       </c>
     </row>
-    <row r="108">
+    <row r="108" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>392</v>
       </c>
       <c r="B108">
-        <v>26.97222222222222</v>
+        <v>26.972222222222221</v>
       </c>
       <c r="C108">
         <v>994</v>
       </c>
     </row>
-    <row r="109">
+    <row r="109" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>393</v>
       </c>
       <c r="B109">
-        <v>27.22222222222222</v>
+        <v>27.222222222222221</v>
       </c>
       <c r="C109">
         <v>994</v>
       </c>
     </row>
-    <row r="110">
+    <row r="110" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>394</v>
       </c>
       <c r="B110">
-        <v>27.47222222222222</v>
+        <v>27.472222222222221</v>
       </c>
       <c r="C110">
         <v>994</v>
       </c>
     </row>
-    <row r="111">
+    <row r="111" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>395</v>
       </c>
       <c r="B111">
-        <v>27.72222222222222</v>
+        <v>27.722222222222221</v>
       </c>
       <c r="C111">
         <v>993</v>
       </c>
     </row>
-    <row r="112">
+    <row r="112" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>396</v>
       </c>
       <c r="B112">
-        <v>27.97222222222222</v>
+        <v>27.972222222222221</v>
       </c>
       <c r="C112">
         <v>993</v>
       </c>
     </row>
-    <row r="113">
+    <row r="113" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>397</v>
       </c>
       <c r="B113">
-        <v>28.22222222222222</v>
+        <v>28.222222222222221</v>
       </c>
       <c r="C113">
         <v>993</v>
       </c>
     </row>
-    <row r="114">
+    <row r="114" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>398</v>
       </c>
       <c r="B114">
-        <v>28.47222222222222</v>
+        <v>28.472222222222221</v>
       </c>
       <c r="C114">
         <v>993</v>
       </c>
     </row>
-    <row r="115">
+    <row r="115" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>399</v>
       </c>
       <c r="B115">
-        <v>28.72222222222222</v>
+        <v>28.722222222222221</v>
       </c>
       <c r="C115">
         <v>993</v>
       </c>
     </row>
-    <row r="116">
+    <row r="116" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>400</v>
       </c>
       <c r="B116">
-        <v>28.97222222222222</v>
+        <v>28.972222222222221</v>
       </c>
       <c r="C116">
         <v>993</v>
       </c>
     </row>
-    <row r="117">
+    <row r="117" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>401</v>
       </c>
       <c r="B117">
-        <v>29.22222222222222</v>
+        <v>29.222222222222221</v>
       </c>
       <c r="C117">
         <v>993</v>
       </c>
     </row>
-    <row r="118">
+    <row r="118" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>402</v>
       </c>
       <c r="B118">
-        <v>29.47222222222222</v>
+        <v>29.472222222222221</v>
       </c>
       <c r="C118">
         <v>993</v>
       </c>
     </row>
-    <row r="119">
+    <row r="119" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>403</v>
       </c>
       <c r="B119">
-        <v>29.72222222222222</v>
+        <v>29.722222222222221</v>
       </c>
       <c r="C119">
         <v>993</v>
       </c>
     </row>
-    <row r="120">
+    <row r="120" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>404</v>
       </c>
       <c r="B120">
-        <v>29.97222222222222</v>
+        <v>29.972222222222221</v>
       </c>
       <c r="C120">
         <v>994</v>
       </c>
     </row>
-    <row r="121">
+    <row r="121" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>405</v>
       </c>
       <c r="B121">
-        <v>30.22222222222222</v>
+        <v>30.222222222222221</v>
       </c>
       <c r="C121">
         <v>993</v>
       </c>
     </row>
-    <row r="122">
+    <row r="122" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>406</v>
       </c>
       <c r="B122">
-        <v>30.47222222222222</v>
+        <v>30.472222222222221</v>
       </c>
       <c r="C122">
         <v>993</v>
       </c>
     </row>
-    <row r="123">
+    <row r="123" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>407</v>
       </c>
       <c r="B123">
-        <v>30.72222222222222</v>
+        <v>30.722222222222221</v>
       </c>
       <c r="C123">
         <v>993</v>
       </c>
     </row>
-    <row r="124">
+    <row r="124" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>408</v>
       </c>
       <c r="B124">
-        <v>30.97222222222222</v>
+        <v>30.972222222222221</v>
       </c>
       <c r="C124">
         <v>993</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C124"/>
+    <ignoredError sqref="A1:C124" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:G1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>284</v>
       </c>
@@ -5409,17 +5437,19 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G1"/>
+    <ignoredError sqref="A1:G1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:DB2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:106" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -5739,7 +5769,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:106" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9846</v>
       </c>
@@ -5774,7 +5804,7 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>45373.65277777778</v>
+        <v>45373.652777777781</v>
       </c>
       <c r="M2" t="s">
         <v>137</v>
@@ -5783,7 +5813,7 @@
         <v>138</v>
       </c>
       <c r="O2">
-        <v>45380.65277777778</v>
+        <v>45380.652777777781</v>
       </c>
       <c r="P2" t="s">
         <v>139</v>
@@ -5864,7 +5894,7 @@
         <v>147</v>
       </c>
       <c r="AS2">
-        <v>19.1</v>
+        <v>19.100000000000001</v>
       </c>
       <c r="AT2">
         <v>31.6</v>
@@ -5969,7 +5999,7 @@
         <v>0</v>
       </c>
       <c r="CB2">
-        <v>0.014</v>
+        <v>1.4E-2</v>
       </c>
       <c r="CC2">
         <v>0</v>
@@ -6011,7 +6041,7 @@
         <v>0</v>
       </c>
       <c r="CP2">
-        <v>0.048</v>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="CQ2">
         <v>0</v>
@@ -6039,17 +6069,19 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:DB2"/>
+    <ignoredError sqref="A1:DB2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:Q12"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>166</v>
       </c>
@@ -6102,7 +6134,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9846</v>
       </c>
@@ -6131,7 +6163,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>9846</v>
       </c>
@@ -6166,7 +6198,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>9846</v>
       </c>
@@ -6195,7 +6227,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>9846</v>
       </c>
@@ -6209,7 +6241,7 @@
         <v>191</v>
       </c>
       <c r="E5">
-        <v>0.014</v>
+        <v>1.4E-2</v>
       </c>
       <c r="F5" t="s">
         <v>187</v>
@@ -6245,7 +6277,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>9846</v>
       </c>
@@ -6259,7 +6291,7 @@
         <v>191</v>
       </c>
       <c r="E6">
-        <v>0.048</v>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="F6" t="s">
         <v>187</v>
@@ -6295,7 +6327,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>9846</v>
       </c>
@@ -6330,7 +6362,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>9846</v>
       </c>
@@ -6377,7 +6409,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>9846</v>
       </c>
@@ -6406,7 +6438,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9846</v>
       </c>
@@ -6441,7 +6473,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>9846</v>
       </c>
@@ -6476,7 +6508,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>9846</v>
       </c>
@@ -6512,17 +6544,19 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q12"/>
+    <ignoredError sqref="A1:Q12" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:J4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>166</v>
       </c>
@@ -6554,7 +6588,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9846</v>
       </c>
@@ -6586,7 +6620,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>9846</v>
       </c>
@@ -6618,7 +6652,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>9846</v>
       </c>
@@ -6651,27 +6685,31 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J4"/>
+    <ignoredError sqref="A1:J4" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1"/>
+    <ignoredError sqref="A1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:J2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>166</v>
       </c>
@@ -6703,7 +6741,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9846</v>
       </c>
@@ -6736,17 +6774,19 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J2"/>
+    <ignoredError sqref="A1:J2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:E2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>166</v>
       </c>
@@ -6763,7 +6803,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9846</v>
       </c>
@@ -6775,27 +6815,31 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E2"/>
+    <ignoredError sqref="A1:E2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1"/>
+    <ignoredError sqref="A1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:P33"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>166</v>
       </c>
@@ -6845,7 +6889,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9846</v>
       </c>
@@ -6858,8 +6902,8 @@
       <c r="D2">
         <v>6821</v>
       </c>
-      <c r="E2">
-        <v>45373.7788425926</v>
+      <c r="E2" s="1">
+        <v>45373.778842592597</v>
       </c>
       <c r="F2" t="s">
         <v>136</v>
@@ -6889,13 +6933,13 @@
         <v>249</v>
       </c>
       <c r="O2">
-        <v>7.5735</v>
+        <v>7.5735000000000001</v>
       </c>
       <c r="P2" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>9846</v>
       </c>
@@ -6908,8 +6952,8 @@
       <c r="D3">
         <v>6821</v>
       </c>
-      <c r="E3">
-        <v>45373.7788425926</v>
+      <c r="E3" s="1">
+        <v>45373.778842592597</v>
       </c>
       <c r="F3" t="s">
         <v>136</v>
@@ -6939,13 +6983,13 @@
         <v>249</v>
       </c>
       <c r="O3">
-        <v>3.435</v>
+        <v>3.4350000000000001</v>
       </c>
       <c r="P3" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>9846</v>
       </c>
@@ -6958,8 +7002,8 @@
       <c r="D4">
         <v>6821</v>
       </c>
-      <c r="E4">
-        <v>45373.7788425926</v>
+      <c r="E4" s="1">
+        <v>45373.778842592597</v>
       </c>
       <c r="F4" t="s">
         <v>136</v>
@@ -6995,7 +7039,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>9846</v>
       </c>
@@ -7008,8 +7052,8 @@
       <c r="D5">
         <v>6821</v>
       </c>
-      <c r="E5">
-        <v>45373.7788425926</v>
+      <c r="E5" s="1">
+        <v>45373.778842592597</v>
       </c>
       <c r="F5" t="s">
         <v>136</v>
@@ -7045,7 +7089,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>9846</v>
       </c>
@@ -7058,8 +7102,8 @@
       <c r="D6">
         <v>6821</v>
       </c>
-      <c r="E6">
-        <v>45373.7788425926</v>
+      <c r="E6" s="1">
+        <v>45373.778842592597</v>
       </c>
       <c r="F6" t="s">
         <v>136</v>
@@ -7095,7 +7139,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>9846</v>
       </c>
@@ -7108,8 +7152,8 @@
       <c r="D7">
         <v>6821</v>
       </c>
-      <c r="E7">
-        <v>45373.7788425926</v>
+      <c r="E7" s="1">
+        <v>45373.778842592597</v>
       </c>
       <c r="F7" t="s">
         <v>136</v>
@@ -7145,7 +7189,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>9846</v>
       </c>
@@ -7158,8 +7202,8 @@
       <c r="D8">
         <v>6821</v>
       </c>
-      <c r="E8">
-        <v>45373.7788425926</v>
+      <c r="E8" s="1">
+        <v>45373.778842592597</v>
       </c>
       <c r="F8" t="s">
         <v>136</v>
@@ -7195,7 +7239,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>9846</v>
       </c>
@@ -7208,8 +7252,8 @@
       <c r="D9">
         <v>6887</v>
       </c>
-      <c r="E9">
-        <v>45376.65851851852</v>
+      <c r="E9" s="1">
+        <v>45373.658518518518</v>
       </c>
       <c r="F9" t="s">
         <v>136</v>
@@ -7239,13 +7283,13 @@
         <v>249</v>
       </c>
       <c r="O9">
-        <v>7.6653</v>
+        <v>7.6653000000000002</v>
       </c>
       <c r="P9" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9846</v>
       </c>
@@ -7258,8 +7302,8 @@
       <c r="D10">
         <v>6887</v>
       </c>
-      <c r="E10">
-        <v>45376.65851851852</v>
+      <c r="E10" s="1">
+        <v>45373.658518518518</v>
       </c>
       <c r="F10" t="s">
         <v>136</v>
@@ -7295,7 +7339,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>9846</v>
       </c>
@@ -7308,8 +7352,8 @@
       <c r="D11">
         <v>6887</v>
       </c>
-      <c r="E11">
-        <v>45376.65851851852</v>
+      <c r="E11" s="1">
+        <v>45373.658518518518</v>
       </c>
       <c r="F11" t="s">
         <v>136</v>
@@ -7339,13 +7383,13 @@
         <v>249</v>
       </c>
       <c r="O11">
-        <v>20.4</v>
+        <v>20.399999999999999</v>
       </c>
       <c r="P11" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>9846</v>
       </c>
@@ -7358,8 +7402,8 @@
       <c r="D12">
         <v>6887</v>
       </c>
-      <c r="E12">
-        <v>45376.65851851852</v>
+      <c r="E12" s="1">
+        <v>45373.658518518518</v>
       </c>
       <c r="F12" t="s">
         <v>136</v>
@@ -7395,7 +7439,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>9846</v>
       </c>
@@ -7408,8 +7452,8 @@
       <c r="D13">
         <v>6887</v>
       </c>
-      <c r="E13">
-        <v>45376.65851851852</v>
+      <c r="E13" s="1">
+        <v>45373.658518518518</v>
       </c>
       <c r="F13" t="s">
         <v>136</v>
@@ -7445,7 +7489,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>9846</v>
       </c>
@@ -7458,8 +7502,8 @@
       <c r="D14">
         <v>6887</v>
       </c>
-      <c r="E14">
-        <v>45376.65851851852</v>
+      <c r="E14" s="1">
+        <v>45373.658518518518</v>
       </c>
       <c r="F14" t="s">
         <v>136</v>
@@ -7489,13 +7533,13 @@
         <v>249</v>
       </c>
       <c r="O14">
-        <v>39.3</v>
+        <v>39.299999999999997</v>
       </c>
       <c r="P14" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>9846</v>
       </c>
@@ -7508,8 +7552,8 @@
       <c r="D15">
         <v>6887</v>
       </c>
-      <c r="E15">
-        <v>45376.65851851852</v>
+      <c r="E15" s="1">
+        <v>45373.658518518518</v>
       </c>
       <c r="F15" t="s">
         <v>136</v>
@@ -7545,7 +7589,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>9846</v>
       </c>
@@ -7558,8 +7602,8 @@
       <c r="D16">
         <v>7410</v>
       </c>
-      <c r="E16">
-        <v>45391.68038194445</v>
+      <c r="E16" s="1">
+        <v>45391.680381944447</v>
       </c>
       <c r="F16" t="s">
         <v>136</v>
@@ -7595,7 +7639,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>9846</v>
       </c>
@@ -7608,8 +7652,8 @@
       <c r="D17">
         <v>7537</v>
       </c>
-      <c r="E17">
-        <v>45394.62240740741</v>
+      <c r="E17" s="1">
+        <v>45394.622407407413</v>
       </c>
       <c r="F17" t="s">
         <v>136</v>
@@ -7645,7 +7689,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>9846</v>
       </c>
@@ -7658,8 +7702,8 @@
       <c r="D18">
         <v>7578</v>
       </c>
-      <c r="E18">
-        <v>45396.72226851852</v>
+      <c r="E18" s="1">
+        <v>45396.722268518519</v>
       </c>
       <c r="F18" t="s">
         <v>136</v>
@@ -7695,7 +7739,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>9846</v>
       </c>
@@ -7708,7 +7752,7 @@
       <c r="D19">
         <v>7579</v>
       </c>
-      <c r="E19">
+      <c r="E19" s="1">
         <v>45396.722604166665</v>
       </c>
       <c r="F19" t="s">
@@ -7745,7 +7789,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>9846</v>
       </c>
@@ -7758,8 +7802,8 @@
       <c r="D20">
         <v>7631</v>
       </c>
-      <c r="E20">
-        <v>45398.89695601852</v>
+      <c r="E20" s="1">
+        <v>45398.896956018521</v>
       </c>
       <c r="F20" t="s">
         <v>136</v>
@@ -7795,7 +7839,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>9846</v>
       </c>
@@ -7808,8 +7852,8 @@
       <c r="D21">
         <v>7631</v>
       </c>
-      <c r="E21">
-        <v>45398.89695601852</v>
+      <c r="E21" s="1">
+        <v>45398.896956018521</v>
       </c>
       <c r="F21" t="s">
         <v>136</v>
@@ -7845,7 +7889,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>9846</v>
       </c>
@@ -7858,8 +7902,8 @@
       <c r="D22">
         <v>7789</v>
       </c>
-      <c r="E22">
-        <v>45406.57679398148</v>
+      <c r="E22" s="1">
+        <v>45406.576793981483</v>
       </c>
       <c r="F22" t="s">
         <v>136</v>
@@ -7895,7 +7939,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>9846</v>
       </c>
@@ -7908,8 +7952,8 @@
       <c r="D23">
         <v>7789</v>
       </c>
-      <c r="E23">
-        <v>45406.57679398148</v>
+      <c r="E23" s="1">
+        <v>45406.576793981483</v>
       </c>
       <c r="F23" t="s">
         <v>136</v>
@@ -7945,7 +7989,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>9846</v>
       </c>
@@ -7958,8 +8002,8 @@
       <c r="D24">
         <v>7789</v>
       </c>
-      <c r="E24">
-        <v>45406.57679398148</v>
+      <c r="E24" s="1">
+        <v>45406.576793981483</v>
       </c>
       <c r="F24" t="s">
         <v>136</v>
@@ -7995,7 +8039,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>9846</v>
       </c>
@@ -8008,8 +8052,8 @@
       <c r="D25">
         <v>7789</v>
       </c>
-      <c r="E25">
-        <v>45406.57679398148</v>
+      <c r="E25" s="1">
+        <v>45406.576793981483</v>
       </c>
       <c r="F25" t="s">
         <v>136</v>
@@ -8045,7 +8089,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>9846</v>
       </c>
@@ -8058,8 +8102,8 @@
       <c r="D26">
         <v>7789</v>
       </c>
-      <c r="E26">
-        <v>45406.57679398148</v>
+      <c r="E26" s="1">
+        <v>45406.576793981483</v>
       </c>
       <c r="F26" t="s">
         <v>136</v>
@@ -8095,7 +8139,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>9846</v>
       </c>
@@ -8108,8 +8152,8 @@
       <c r="D27">
         <v>7789</v>
       </c>
-      <c r="E27">
-        <v>45406.57679398148</v>
+      <c r="E27" s="1">
+        <v>45406.576793981483</v>
       </c>
       <c r="F27" t="s">
         <v>136</v>
@@ -8145,7 +8189,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>9846</v>
       </c>
@@ -8158,8 +8202,8 @@
       <c r="D28">
         <v>7789</v>
       </c>
-      <c r="E28">
-        <v>45406.57679398148</v>
+      <c r="E28" s="1">
+        <v>45406.576793981483</v>
       </c>
       <c r="F28" t="s">
         <v>136</v>
@@ -8195,7 +8239,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>9846</v>
       </c>
@@ -8208,8 +8252,8 @@
       <c r="D29">
         <v>7789</v>
       </c>
-      <c r="E29">
-        <v>45406.57679398148</v>
+      <c r="E29" s="1">
+        <v>45406.576793981483</v>
       </c>
       <c r="F29" t="s">
         <v>136</v>
@@ -8245,7 +8289,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>9846</v>
       </c>
@@ -8258,8 +8302,8 @@
       <c r="D30">
         <v>7789</v>
       </c>
-      <c r="E30">
-        <v>45406.57679398148</v>
+      <c r="E30" s="1">
+        <v>45406.576793981483</v>
       </c>
       <c r="F30" t="s">
         <v>136</v>
@@ -8295,7 +8339,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>9846</v>
       </c>
@@ -8308,8 +8352,8 @@
       <c r="D31">
         <v>7789</v>
       </c>
-      <c r="E31">
-        <v>45406.57679398148</v>
+      <c r="E31" s="1">
+        <v>45406.576793981483</v>
       </c>
       <c r="F31" t="s">
         <v>136</v>
@@ -8345,7 +8389,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>9846</v>
       </c>
@@ -8358,8 +8402,8 @@
       <c r="D32">
         <v>7789</v>
       </c>
-      <c r="E32">
-        <v>45406.57679398148</v>
+      <c r="E32" s="1">
+        <v>45406.576793981483</v>
       </c>
       <c r="F32" t="s">
         <v>136</v>
@@ -8395,7 +8439,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>9846</v>
       </c>
@@ -8408,8 +8452,8 @@
       <c r="D33">
         <v>7789</v>
       </c>
-      <c r="E33">
-        <v>45406.57679398148</v>
+      <c r="E33" s="1">
+        <v>45406.576793981483</v>
       </c>
       <c r="F33" t="s">
         <v>136</v>
@@ -8446,8 +8490,9 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P33"/>
+    <ignoredError sqref="A1:P8 A16:P33 A9:D9 F9:P9 A10:D15 F10:P15" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>